--- a/artfynd/A 32821-2025 artfynd.xlsx
+++ b/artfynd/A 32821-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,6 +894,123 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126632366</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Merehäll, Merehäll, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>579412</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6314364</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ser den här ibland.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32821-2025 artfynd.xlsx
+++ b/artfynd/A 32821-2025 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>127014332</v>
       </c>
       <c r="B5" t="n">
-        <v>95964</v>
+        <v>96039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32821-2025 artfynd.xlsx
+++ b/artfynd/A 32821-2025 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>127014332</v>
       </c>
       <c r="B5" t="n">
-        <v>96039</v>
+        <v>96045</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32821-2025 artfynd.xlsx
+++ b/artfynd/A 32821-2025 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>127014332</v>
       </c>
       <c r="B5" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32821-2025 artfynd.xlsx
+++ b/artfynd/A 32821-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1113,6 +1113,142 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127503411</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dansehäll, Dansehäll, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>579489</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6314255</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ser Spillkråka frekvent i området.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32821-2025 artfynd.xlsx
+++ b/artfynd/A 32821-2025 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>127014332</v>
       </c>
       <c r="B5" t="n">
-        <v>96046</v>
+        <v>96050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32821-2025 artfynd.xlsx
+++ b/artfynd/A 32821-2025 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>127014332</v>
       </c>
       <c r="B5" t="n">
-        <v>96050</v>
+        <v>96052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>127503411</v>
       </c>
       <c r="B6" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32821-2025 artfynd.xlsx
+++ b/artfynd/A 32821-2025 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>127503411</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32821-2025 artfynd.xlsx
+++ b/artfynd/A 32821-2025 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>127503411</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32821-2025 artfynd.xlsx
+++ b/artfynd/A 32821-2025 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>127014332</v>
       </c>
       <c r="B5" t="n">
-        <v>96052</v>
+        <v>96039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
